--- a/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
+++ b/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
@@ -1432,52 +1432,52 @@
         <v>0</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AD5" s="7" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="7" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AH5" s="7" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AL5" s="7" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="6" t="n">
         <v>0</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="AR5" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AT5" s="7" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="AU5" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AV5" s="6" t="n">
         <v>0</v>
@@ -1525,9 +1525,19 @@
       <c r="BI5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="6" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>간호학부</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -1762,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="X7" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="7" t="n">
         <v>0</v>
@@ -1780,34 +1790,34 @@
         <v>0</v>
       </c>
       <c r="AD7" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="6" t="n">
         <v>0</v>
@@ -1822,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="AR7" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT7" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU7" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV7" s="6" t="n">
         <v>0</v>
@@ -1855,9 +1865,19 @@
       <c r="BI7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="6" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>치위생과</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -2098,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="7" t="n">
         <v>0</v>
@@ -2110,10 +2130,10 @@
         <v>0</v>
       </c>
       <c r="AD9" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="6" t="n">
         <v>0</v>
@@ -2122,19 +2142,19 @@
         <v>0</v>
       </c>
       <c r="AH9" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="7" t="n">
         <v>0</v>
@@ -2152,13 +2172,13 @@
         <v>0</v>
       </c>
       <c r="AR9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU9" s="7" t="n">
         <v>0</v>
@@ -2185,9 +2205,19 @@
       <c r="BI9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>응급구조과</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -2327,8 +2357,12 @@
       <c r="AV10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AW10" s="7" t="n"/>
-      <c r="AX10" s="7" t="n"/>
+      <c r="AW10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AY10" s="7" t="n"/>
       <c r="AZ10" s="6" t="n"/>
       <c r="BA10" s="7" t="n"/>
@@ -2448,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="7" t="n">
         <v>0</v>
@@ -2511,9 +2545,19 @@
       <c r="BI11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="6" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>호텔조리&amp;베이커리과</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -2694,10 +2738,10 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
@@ -2766,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="7" t="n">
         <v>0</v>
@@ -2778,10 +2822,10 @@
         <v>0</v>
       </c>
       <c r="AH13" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="6" t="n">
         <v>0</v>
@@ -2841,9 +2885,19 @@
       <c r="BI13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>호텔소믈리에&amp;바리스타과</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -3002,7 +3056,11 @@
       <c r="BI14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>외식&amp;디저트창업과</t>
@@ -3084,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="7" t="n">
         <v>0</v>
@@ -3096,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="6" t="n">
         <v>0</v>
@@ -3108,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" s="6" t="n">
         <v>0</v>
@@ -3171,9 +3229,19 @@
       <c r="BI15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="6" t="n"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>외식&amp;디저트창업과</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -3415,13 +3483,13 @@
         <v>0</v>
       </c>
       <c r="Y17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
         <v>0</v>
@@ -3430,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="7" t="n">
         <v>0</v>
@@ -3439,13 +3507,13 @@
         <v>0</v>
       </c>
       <c r="AG17" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="6" t="n">
         <v>0</v>
@@ -3505,9 +3573,19 @@
       <c r="BI17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="6" t="n"/>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>예체능계열</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>토탈미용과</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -3764,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19" s="7" t="n">
         <v>0</v>
@@ -3776,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="7" t="n">
         <v>0</v>
@@ -3839,9 +3917,19 @@
       <c r="BI19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>인문사회계열</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>사회복지서비스과</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -4056,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="7" t="n">
         <v>0</v>
@@ -4086,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="7" t="n">
         <v>0</v>
@@ -4098,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="7" t="n">
         <v>0</v>
@@ -4107,13 +4195,13 @@
         <v>0</v>
       </c>
       <c r="AG21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" s="6" t="n">
         <v>0</v>
@@ -4173,9 +4261,19 @@
       <c r="BI21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="6" t="n"/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>예체능계열</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>생활문화음악과</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -4344,10 +4442,10 @@
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="29" t="n"/>
       <c r="F23" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -4374,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="12" t="n">
         <v>0</v>
@@ -4398,52 +4496,52 @@
         <v>0</v>
       </c>
       <c r="X23" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD23" s="12" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AH23" s="12" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ23" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL23" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="AM23" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN23" s="12" t="n">
         <v>0</v>
@@ -4458,16 +4556,16 @@
         <v>0</v>
       </c>
       <c r="AR23" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AS23" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT23" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="AU23" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AV23" s="12" t="n">
         <v>0</v>

--- a/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
+++ b/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
@@ -1696,7 +1696,11 @@
       <c r="BI6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>치위생과</t>
@@ -2036,7 +2040,11 @@
       <c r="BI8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>응급구조과</t>
@@ -2376,7 +2384,11 @@
       <c r="BI10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>호텔조리&amp;베이커리과</t>
@@ -2716,7 +2728,11 @@
       <c r="BI12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>자연과학계열</t>
+        </is>
+      </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>호텔소믈리에&amp;바리스타과</t>

--- a/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
+++ b/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
@@ -1432,52 +1432,52 @@
         <v>0</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Y5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="7" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="AA5" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AB5" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AD5" s="7" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AE5" s="7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF5" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG5" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH5" s="7" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="AI5" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AK5" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL5" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AM5" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN5" s="6" t="n">
         <v>0</v>
@@ -1492,16 +1492,16 @@
         <v>0</v>
       </c>
       <c r="AR5" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS5" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT5" s="7" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU5" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV5" s="6" t="n">
         <v>0</v>
@@ -1512,32 +1512,44 @@
       <c r="AX5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY5" s="7" t="n"/>
-      <c r="AZ5" s="6" t="n"/>
-      <c r="BA5" s="7" t="n"/>
-      <c r="BB5" s="7" t="n"/>
-      <c r="BC5" s="7" t="n"/>
-      <c r="BD5" s="6" t="n"/>
-      <c r="BE5" s="6" t="n"/>
-      <c r="BF5" s="6" t="n"/>
-      <c r="BG5" s="37" t="n"/>
-      <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="10" t="n"/>
+      <c r="AY5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE5" s="6" t="n">
+        <v>496</v>
+      </c>
+      <c r="BF5" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="BG5" s="37" t="n">
+        <v>551.11</v>
+      </c>
+      <c r="BH5" s="9" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="BI5" s="10" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>간호학부</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>4</v>
-      </c>
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -1683,24 +1695,42 @@
       <c r="AX6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY6" s="7" t="n"/>
-      <c r="AZ6" s="6" t="n"/>
-      <c r="BA6" s="7" t="n"/>
-      <c r="BB6" s="7" t="n"/>
-      <c r="BC6" s="7" t="n"/>
-      <c r="BD6" s="6" t="n"/>
-      <c r="BE6" s="6" t="n"/>
-      <c r="BF6" s="6" t="n"/>
-      <c r="BG6" s="9" t="n"/>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="10" t="n"/>
+      <c r="AY6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>치위생과</t>
@@ -1776,16 +1806,16 @@
         <v>0</v>
       </c>
       <c r="X7" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB7" s="7" t="n">
         <v>0</v>
@@ -1794,34 +1824,34 @@
         <v>0</v>
       </c>
       <c r="AD7" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="6" t="n">
         <v>0</v>
@@ -1836,16 +1866,16 @@
         <v>0</v>
       </c>
       <c r="AR7" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" s="6" t="n">
         <v>0</v>
@@ -1856,32 +1886,44 @@
       <c r="AX7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY7" s="7" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="7" t="n"/>
-      <c r="BB7" s="7" t="n"/>
-      <c r="BC7" s="7" t="n"/>
-      <c r="BD7" s="6" t="n"/>
-      <c r="BE7" s="6" t="n"/>
-      <c r="BF7" s="6" t="n"/>
-      <c r="BG7" s="37" t="n"/>
-      <c r="BH7" s="37" t="n"/>
-      <c r="BI7" s="10" t="n"/>
+      <c r="AY7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG7" s="37" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="BH7" s="37" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI7" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>치위생과</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>3</v>
-      </c>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -2027,24 +2069,42 @@
       <c r="AX8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY8" s="7" t="n"/>
-      <c r="AZ8" s="6" t="n"/>
-      <c r="BA8" s="7" t="n"/>
-      <c r="BB8" s="7" t="n"/>
-      <c r="BC8" s="7" t="n"/>
-      <c r="BD8" s="6" t="n"/>
-      <c r="BE8" s="6" t="n"/>
-      <c r="BF8" s="6" t="n"/>
-      <c r="BG8" s="9" t="n"/>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="10" t="n"/>
+      <c r="AY8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>응급구조과</t>
@@ -2126,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="7" t="n">
         <v>0</v>
@@ -2138,31 +2198,31 @@
         <v>0</v>
       </c>
       <c r="AD9" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AL9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="7" t="n">
         <v>0</v>
@@ -2180,13 +2240,13 @@
         <v>0</v>
       </c>
       <c r="AR9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AT9" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU9" s="7" t="n">
         <v>0</v>
@@ -2200,32 +2260,44 @@
       <c r="AX9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY9" s="7" t="n"/>
-      <c r="AZ9" s="6" t="n"/>
-      <c r="BA9" s="7" t="n"/>
-      <c r="BB9" s="7" t="n"/>
-      <c r="BC9" s="7" t="n"/>
-      <c r="BD9" s="6" t="n"/>
-      <c r="BE9" s="6" t="n"/>
-      <c r="BF9" s="6" t="n"/>
-      <c r="BG9" s="37" t="n"/>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="10" t="n"/>
+      <c r="AY9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE9" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG9" s="37" t="n">
+        <v>850</v>
+      </c>
+      <c r="BH9" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="BI9" s="10" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>응급구조과</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>3</v>
-      </c>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -2371,24 +2443,42 @@
       <c r="AX10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY10" s="7" t="n"/>
-      <c r="AZ10" s="6" t="n"/>
-      <c r="BA10" s="7" t="n"/>
-      <c r="BB10" s="7" t="n"/>
-      <c r="BC10" s="7" t="n"/>
-      <c r="BD10" s="6" t="n"/>
-      <c r="BE10" s="6" t="n"/>
-      <c r="BF10" s="6" t="n"/>
-      <c r="BG10" s="9" t="n"/>
-      <c r="BH10" s="9" t="n"/>
-      <c r="BI10" s="10" t="n"/>
+      <c r="AY10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>호텔조리&amp;베이커리과</t>
@@ -2410,7 +2500,7 @@
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -2494,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI11" s="7" t="n">
         <v>0</v>
@@ -2544,32 +2634,44 @@
       <c r="AX11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" s="7" t="n"/>
-      <c r="AZ11" s="6" t="n"/>
-      <c r="BA11" s="7" t="n"/>
-      <c r="BB11" s="7" t="n"/>
-      <c r="BC11" s="7" t="n"/>
-      <c r="BD11" s="6" t="n"/>
-      <c r="BE11" s="6" t="n"/>
-      <c r="BF11" s="6" t="n"/>
-      <c r="BG11" s="37" t="n"/>
-      <c r="BH11" s="9" t="n"/>
-      <c r="BI11" s="10" t="n"/>
+      <c r="AY11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="37" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>호텔조리&amp;베이커리과</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -2715,24 +2817,42 @@
       <c r="AX12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" s="7" t="n"/>
-      <c r="AZ12" s="6" t="n"/>
-      <c r="BA12" s="7" t="n"/>
-      <c r="BB12" s="7" t="n"/>
-      <c r="BC12" s="7" t="n"/>
-      <c r="BD12" s="6" t="n"/>
-      <c r="BE12" s="6" t="n"/>
-      <c r="BF12" s="6" t="n"/>
-      <c r="BG12" s="9" t="n"/>
-      <c r="BH12" s="9" t="n"/>
-      <c r="BI12" s="10" t="n"/>
+      <c r="AY12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>호텔소믈리에&amp;바리스타과</t>
@@ -2754,7 +2874,7 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -2826,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" s="7" t="n">
         <v>0</v>
@@ -2835,13 +2955,13 @@
         <v>0</v>
       </c>
       <c r="AG13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="6" t="n">
         <v>0</v>
@@ -2888,32 +3008,44 @@
       <c r="AX13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY13" s="7" t="n"/>
-      <c r="AZ13" s="6" t="n"/>
-      <c r="BA13" s="7" t="n"/>
-      <c r="BB13" s="7" t="n"/>
-      <c r="BC13" s="7" t="n"/>
-      <c r="BD13" s="6" t="n"/>
-      <c r="BE13" s="6" t="n"/>
-      <c r="BF13" s="6" t="n"/>
-      <c r="BG13" s="37" t="n"/>
-      <c r="BH13" s="37" t="n"/>
-      <c r="BI13" s="10" t="n"/>
+      <c r="AY13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG13" s="37" t="n">
+        <v>200</v>
+      </c>
+      <c r="BH13" s="37" t="n">
+        <v>100</v>
+      </c>
+      <c r="BI13" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>호텔소믈리에&amp;바리스타과</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -3059,24 +3191,42 @@
       <c r="AX14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" s="7" t="n"/>
-      <c r="AZ14" s="6" t="n"/>
-      <c r="BA14" s="7" t="n"/>
-      <c r="BB14" s="7" t="n"/>
-      <c r="BC14" s="7" t="n"/>
-      <c r="BD14" s="6" t="n"/>
-      <c r="BE14" s="6" t="n"/>
-      <c r="BF14" s="6" t="n"/>
-      <c r="BG14" s="9" t="n"/>
-      <c r="BH14" s="9" t="n"/>
-      <c r="BI14" s="10" t="n"/>
+      <c r="AY14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>외식&amp;디저트창업과</t>
@@ -3158,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="7" t="n">
         <v>0</v>
@@ -3170,22 +3320,22 @@
         <v>0</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AG15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="6" t="n">
         <v>0</v>
@@ -3212,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="AR15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS15" s="7" t="n">
         <v>0</v>
@@ -3232,32 +3382,44 @@
       <c r="AX15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" s="7" t="n"/>
-      <c r="AZ15" s="6" t="n"/>
-      <c r="BA15" s="7" t="n"/>
-      <c r="BB15" s="7" t="n"/>
-      <c r="BC15" s="7" t="n"/>
-      <c r="BD15" s="6" t="n"/>
-      <c r="BE15" s="6" t="n"/>
-      <c r="BF15" s="6" t="n"/>
-      <c r="BG15" s="37" t="n"/>
-      <c r="BH15" s="9" t="n"/>
-      <c r="BI15" s="10" t="n"/>
+      <c r="AY15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE15" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG15" s="37" t="n">
+        <v>2800</v>
+      </c>
+      <c r="BH15" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="BI15" s="10" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>자연과학계열</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>외식&amp;디저트창업과</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -3403,17 +3565,39 @@
       <c r="AX16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" s="7" t="n"/>
-      <c r="AZ16" s="6" t="n"/>
-      <c r="BA16" s="7" t="n"/>
-      <c r="BB16" s="7" t="n"/>
-      <c r="BC16" s="7" t="n"/>
-      <c r="BD16" s="6" t="n"/>
-      <c r="BE16" s="6" t="n"/>
-      <c r="BF16" s="6" t="n"/>
-      <c r="BG16" s="9" t="n"/>
-      <c r="BH16" s="9" t="n"/>
-      <c r="BI16" s="10" t="n"/>
+      <c r="AY16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3502,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="Z17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="7" t="n">
         <v>0</v>
@@ -3514,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE17" s="7" t="n">
         <v>0</v>
@@ -3523,13 +3707,13 @@
         <v>0</v>
       </c>
       <c r="AG17" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH17" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI17" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ17" s="6" t="n">
         <v>0</v>
@@ -3576,32 +3760,44 @@
       <c r="AX17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" s="7" t="n"/>
-      <c r="AZ17" s="6" t="n"/>
-      <c r="BA17" s="7" t="n"/>
-      <c r="BB17" s="7" t="n"/>
-      <c r="BC17" s="7" t="n"/>
-      <c r="BD17" s="6" t="n"/>
-      <c r="BE17" s="6" t="n"/>
-      <c r="BF17" s="6" t="n"/>
-      <c r="BG17" s="37" t="n"/>
-      <c r="BH17" s="9" t="n"/>
-      <c r="BI17" s="10" t="n"/>
+      <c r="AY17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF17" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="10" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>예체능계열</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>토탈미용과</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -3747,17 +3943,39 @@
       <c r="AX18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" s="7" t="n"/>
-      <c r="AZ18" s="6" t="n"/>
-      <c r="BA18" s="7" t="n"/>
-      <c r="BB18" s="7" t="n"/>
-      <c r="BC18" s="7" t="n"/>
-      <c r="BD18" s="6" t="n"/>
-      <c r="BE18" s="6" t="n"/>
-      <c r="BF18" s="6" t="n"/>
-      <c r="BG18" s="9" t="n"/>
-      <c r="BH18" s="9" t="n"/>
-      <c r="BI18" s="10" t="n"/>
+      <c r="AY18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3858,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" s="7" t="n">
         <v>0</v>
@@ -3870,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI19" s="7" t="n">
         <v>0</v>
@@ -3920,32 +4138,44 @@
       <c r="AX19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" s="7" t="n"/>
-      <c r="AZ19" s="6" t="n"/>
-      <c r="BA19" s="7" t="n"/>
-      <c r="BB19" s="7" t="n"/>
-      <c r="BC19" s="7" t="n"/>
-      <c r="BD19" s="6" t="n"/>
-      <c r="BE19" s="6" t="n"/>
-      <c r="BF19" s="6" t="n"/>
-      <c r="BG19" s="9" t="n"/>
-      <c r="BH19" s="9" t="n"/>
-      <c r="BI19" s="10" t="n"/>
+      <c r="AY19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>인문사회계열</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>사회복지서비스과</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -4091,17 +4321,39 @@
       <c r="AX20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" s="7" t="n"/>
-      <c r="AZ20" s="6" t="n"/>
-      <c r="BA20" s="7" t="n"/>
-      <c r="BB20" s="7" t="n"/>
-      <c r="BC20" s="7" t="n"/>
-      <c r="BD20" s="6" t="n"/>
-      <c r="BE20" s="6" t="n"/>
-      <c r="BF20" s="6" t="n"/>
-      <c r="BG20" s="9" t="n"/>
-      <c r="BH20" s="9" t="n"/>
-      <c r="BI20" s="10" t="n"/>
+      <c r="AY20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -4160,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="7" t="n">
         <v>0</v>
@@ -4190,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="7" t="n">
         <v>0</v>
@@ -4202,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" s="7" t="n">
         <v>0</v>
@@ -4211,13 +4463,13 @@
         <v>0</v>
       </c>
       <c r="AG21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="6" t="n">
         <v>0</v>
@@ -4264,32 +4516,44 @@
       <c r="AX21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY21" s="7" t="n"/>
-      <c r="AZ21" s="6" t="n"/>
-      <c r="BA21" s="7" t="n"/>
-      <c r="BB21" s="7" t="n"/>
-      <c r="BC21" s="7" t="n"/>
-      <c r="BD21" s="6" t="n"/>
-      <c r="BE21" s="6" t="n"/>
-      <c r="BF21" s="6" t="n"/>
-      <c r="BG21" s="9" t="n"/>
-      <c r="BH21" s="9" t="n"/>
-      <c r="BI21" s="10" t="n"/>
+      <c r="AY21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="10" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>예체능계열</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>생활문화음악과</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="inlineStr">
         <is>
           <t>야간</t>
@@ -4435,17 +4699,39 @@
       <c r="AX22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" s="7" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="7" t="n"/>
-      <c r="BB22" s="7" t="n"/>
-      <c r="BC22" s="7" t="n"/>
-      <c r="BD22" s="6" t="n"/>
-      <c r="BE22" s="6" t="n"/>
-      <c r="BF22" s="6" t="n"/>
-      <c r="BG22" s="9" t="n"/>
-      <c r="BH22" s="9" t="n"/>
-      <c r="BI22" s="10" t="n"/>
+      <c r="AY22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
@@ -4458,7 +4744,7 @@
       <c r="D23" s="28" t="n"/>
       <c r="E23" s="29" t="n"/>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -4488,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="12" t="n">
         <v>0</v>
@@ -4512,52 +4798,52 @@
         <v>0</v>
       </c>
       <c r="X23" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB23" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD23" s="12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="AE23" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AF23" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG23" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH23" s="12" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="AI23" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL23" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AM23" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN23" s="12" t="n">
         <v>0</v>
@@ -4572,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="AR23" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS23" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT23" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU23" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV23" s="12" t="n">
         <v>0</v>
@@ -4592,17 +4878,39 @@
       <c r="AX23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" s="12" t="n"/>
-      <c r="AZ23" s="12" t="n"/>
-      <c r="BA23" s="12" t="n"/>
-      <c r="BB23" s="12" t="n"/>
-      <c r="BC23" s="12" t="n"/>
-      <c r="BD23" s="12" t="n"/>
-      <c r="BE23" s="12" t="n"/>
-      <c r="BF23" s="12" t="n"/>
-      <c r="BG23" s="12" t="n"/>
-      <c r="BH23" s="12" t="n"/>
-      <c r="BI23" s="12" t="n"/>
+      <c r="AY23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="BE23" s="12" t="n">
+        <v>702</v>
+      </c>
+      <c r="BF23" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="BG23" s="12" t="n">
+        <v>788.76</v>
+      </c>
+      <c r="BH23" s="12" t="n">
+        <v>157.3</v>
+      </c>
+      <c r="BI23" s="12" t="n">
+        <v>-51</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="32">
